--- a/W/A2Pico2LiteW_CPL.xlsx
+++ b/W/A2Pico2LiteW_CPL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2Pico2LiteWH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2Pico2LiteW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C806830D-ED1A-45AE-A0BC-06D5457C450D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C4D1F6-5156-40DA-A571-44E525660E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>Designator</t>
   </si>
@@ -62,21 +62,6 @@
     <t>R2</t>
   </si>
   <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
@@ -93,6 +78,12 @@
   </si>
   <si>
     <t>H3</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>C2</t>
   </si>
 </sst>
 </file>
@@ -471,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.36328125" customWidth="1"/>
@@ -500,7 +491,7 @@
     </row>
     <row r="2" spans="1:13" ht="16" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B2" s="4">
         <v>170.82419999999999</v>
@@ -523,21 +514,21 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="2">
-        <v>161.90299999999999</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-116.03545</v>
+    <row r="3" spans="1:13" ht="16" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="4">
+        <v>132.6388</v>
+      </c>
+      <c r="C3" s="4">
+        <v>-113.51260000000001</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2">
-        <v>0</v>
+      <c r="E3" s="4">
+        <v>-90</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -550,13 +541,13 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
-        <v>161.89959999999999</v>
+        <v>161.90299999999999</v>
       </c>
       <c r="C4" s="2">
-        <v>-112.90300000000001</v>
+        <v>-116.03545</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -575,13 +566,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
-        <v>170.82419999999999</v>
+        <v>161.89959999999999</v>
       </c>
       <c r="C5" s="2">
-        <v>-116.01005000000001</v>
+        <v>-112.90300000000001</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -600,13 +591,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>141.47800000000001</v>
+        <v>170.82419999999999</v>
       </c>
       <c r="C6" s="2">
-        <v>-86.985150000000004</v>
+        <v>-116.01005000000001</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -625,13 +616,13 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2">
         <v>141.47800000000001</v>
       </c>
       <c r="C7" s="2">
-        <v>-104.76515000000001</v>
+        <v>-86.985150000000004</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -650,13 +641,13 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2">
-        <v>146.96440000000001</v>
+        <v>141.47800000000001</v>
       </c>
       <c r="C8" s="2">
-        <v>-115.6208</v>
+        <v>-104.76515000000001</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -664,6 +655,7 @@
       <c r="E8" s="2">
         <v>0</v>
       </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -674,13 +666,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2">
-        <v>127.4318</v>
+        <v>153.6446</v>
       </c>
       <c r="C9" s="2">
-        <v>-115.6208</v>
+        <v>-115.64619999999999</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -698,13 +690,13 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2">
-        <v>139.77619999999999</v>
+        <v>153.6446</v>
       </c>
       <c r="C10" s="2">
-        <v>-115.6208</v>
+        <v>-114.57940000000001</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -721,20 +713,20 @@
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4">
-        <v>153.6446</v>
-      </c>
-      <c r="C11" s="4">
-        <v>-115.64619999999999</v>
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2">
+        <v>129.87020000000001</v>
+      </c>
+      <c r="C11" s="2">
+        <v>-114.50320000000001</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="4">
-        <v>0</v>
+      <c r="E11" s="2">
+        <v>-90</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -744,78 +736,6 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4">
-        <v>142.90039999999999</v>
-      </c>
-      <c r="C12" s="4">
-        <v>-115.6208</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4">
-        <v>131.52119999999999</v>
-      </c>
-      <c r="C13" s="4">
-        <v>-115.64619999999999</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4">
-        <v>135.20419999999999</v>
-      </c>
-      <c r="C14" s="4">
-        <v>-115.6208</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/W/A2Pico2LiteW_CPL.xlsx
+++ b/W/A2Pico2LiteW_CPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2Pico2LiteW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C4D1F6-5156-40DA-A571-44E525660E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C35E81-5EE0-4D9E-A845-573956E319C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>Designator</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>C2</t>
+  </si>
+  <si>
+    <t>R3</t>
   </si>
 </sst>
 </file>
@@ -462,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.36328125" customWidth="1"/>
@@ -714,19 +717,19 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2">
-        <v>129.87020000000001</v>
+        <v>153.6446</v>
       </c>
       <c r="C11" s="2">
-        <v>-114.50320000000001</v>
+        <v>-116.71299999999999</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -736,6 +739,30 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2">
+        <v>129.87020000000001</v>
+      </c>
+      <c r="C12" s="2">
+        <v>-114.50320000000001</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-90</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
